--- a/results/06-2026/beta/inputs-06-2026.xlsx
+++ b/results/06-2026/beta/inputs-06-2026.xlsx
@@ -3960,7 +3960,7 @@
         <v>1949.7</v>
       </c>
       <c r="N22" t="n">
-        <v>371.652997</v>
+        <v>402.652997</v>
       </c>
       <c r="O22" t="n">
         <v>79.2681428571429</v>
@@ -4118,7 +4118,7 @@
         <v>1956.4</v>
       </c>
       <c r="N23" t="n">
-        <v>347.8256195</v>
+        <v>378.8256195</v>
       </c>
       <c r="O23" t="n">
         <v>75.1961428571429</v>
@@ -4276,7 +4276,7 @@
         <v>1989.7</v>
       </c>
       <c r="N24" t="n">
-        <v>373.806928</v>
+        <v>310.806928</v>
       </c>
       <c r="O24" t="n">
         <v>75.1961428571429</v>
@@ -4434,7 +4434,7 @@
         <v>1971.8</v>
       </c>
       <c r="N25" t="n">
-        <v>354.1033188</v>
+        <v>291.1033188</v>
       </c>
       <c r="O25" t="n">
         <v>75.1961428571429</v>
@@ -4592,7 +4592,7 @@
         <v>1986.8</v>
       </c>
       <c r="N26" t="n">
-        <v>309.279</v>
+        <v>299.279</v>
       </c>
       <c r="O26" t="n">
         <v>75.1961428571429</v>
@@ -4750,7 +4750,7 @@
         <v>1993.22590350582</v>
       </c>
       <c r="N27" t="n">
-        <v>289.298764494522</v>
+        <v>299.298764494522</v>
       </c>
       <c r="O27" t="n">
         <v>75.1961428571429</v>
@@ -4908,7 +4908,7 @@
         <v>1995.8134991428</v>
       </c>
       <c r="N28" t="n">
-        <v>293.149342835201</v>
+        <v>303.149342835201</v>
       </c>
       <c r="O28" t="n">
         <v>75.1961428571429</v>
@@ -5066,7 +5066,7 @@
         <v>2008.16227191654</v>
       </c>
       <c r="N29" t="n">
-        <v>295.028009083171</v>
+        <v>305.028009083171</v>
       </c>
       <c r="O29" t="n">
         <v>75.1961428571429</v>
@@ -5224,7 +5224,7 @@
         <v>2019.41841567176</v>
       </c>
       <c r="N30" t="n">
-        <v>297.93504</v>
+        <v>307.93504</v>
       </c>
       <c r="O30" t="n">
         <v>75.1961428571429</v>
@@ -5382,7 +5382,7 @@
         <v>2029.86829015562</v>
       </c>
       <c r="N31" t="n">
-        <v>300.870715074303</v>
+        <v>310.870715074303</v>
       </c>
       <c r="O31" t="n">
         <v>75.1961428571429</v>
@@ -5540,7 +5540,7 @@
         <v>2040.8916978889</v>
       </c>
       <c r="N32" t="n">
-        <v>303.835316548609</v>
+        <v>313.835316548609</v>
       </c>
       <c r="O32" t="n">
         <v>75.1961428571429</v>
@@ -5698,7 +5698,7 @@
         <v>2046.64306409843</v>
       </c>
       <c r="N33" t="n">
-        <v>306.829129446497</v>
+        <v>316.829129446497</v>
       </c>
       <c r="O33" t="n">
         <v>75.1961428571429</v>
@@ -5856,7 +5856,7 @@
         <v>2050.39853806318</v>
       </c>
       <c r="N34" t="n">
-        <v>309.8524416</v>
+        <v>319.8524416</v>
       </c>
       <c r="O34" t="n">
         <v>75.1961428571429</v>

--- a/results/06-2026/beta/inputs-06-2026.xlsx
+++ b/results/06-2026/beta/inputs-06-2026.xlsx
@@ -4759,7 +4759,7 @@
         <v>3462.63828806306</v>
       </c>
       <c r="Q27" t="n">
-        <v>5016.82407316799</v>
+        <v>5034.82407316799</v>
       </c>
       <c r="R27" t="n">
         <v>2636.67277279961</v>
@@ -4816,7 +4816,7 @@
         <v>345.800981275389</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2948.33688878016</v>
+        <v>-2950.49688878016</v>
       </c>
       <c r="AK27" t="n">
         <v>-1520.57073273595</v>
@@ -4917,7 +4917,7 @@
         <v>3496.13488552031</v>
       </c>
       <c r="Q28" t="n">
-        <v>5054.29727260192</v>
+        <v>5072.3688445901</v>
       </c>
       <c r="R28" t="n">
         <v>2666.55786673422</v>
@@ -4974,7 +4974,7 @@
         <v>351.399497154</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-2979.11656149239</v>
+        <v>-2983.44515013097</v>
       </c>
       <c r="AK28" t="n">
         <v>-1540.85167674406</v>
@@ -5075,7 +5075,7 @@
         <v>3526.99675561438</v>
       </c>
       <c r="Q29" t="n">
-        <v>5087.75196760069</v>
+        <v>5105.89539616312</v>
       </c>
       <c r="R29" t="n">
         <v>2694.62842095072</v>
@@ -5132,7 +5132,7 @@
         <v>354.271506931401</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-3013.21935321439</v>
+        <v>-3018.64515328046</v>
       </c>
       <c r="AK29" t="n">
         <v>-1559.81072089017</v>
@@ -5290,7 +5290,7 @@
         <v>355.632237528028</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-3068.49028318578</v>
+        <v>-3072.83178893256</v>
       </c>
       <c r="AK30" t="n">
         <v>-1578.64108314823</v>
@@ -5448,7 +5448,7 @@
         <v>356.997746402807</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-3113.06700025285</v>
+        <v>-3116.31990028589</v>
       </c>
       <c r="AK31" t="n">
         <v>-1597.04323859381</v>
@@ -5606,7 +5606,7 @@
         <v>358.575658685331</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3137.71870416414</v>
+        <v>-3140.97160419717</v>
       </c>
       <c r="AK32" t="n">
         <v>-1615.12920029267</v>
@@ -5764,7 +5764,7 @@
         <v>365.20640021081</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-3160.25881752647</v>
+        <v>-3163.51171755951</v>
       </c>
       <c r="AK33" t="n">
         <v>-1632.22206089396</v>
@@ -5922,7 +5922,7 @@
         <v>373.030059953625</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-3194.97444411764</v>
+        <v>-3198.22734415068</v>
       </c>
       <c r="AK34" t="n">
         <v>-1649.45008021301</v>
